--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SANDÁ C.B. L´HOSPITALET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SANDÁ C.B. L´HOSPITALET.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2765</v>
+        <v>8.213900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2211</v>
+        <v>12.5552</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9447</v>
+        <v>-4.3412</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8344</v>
+        <v>0.7567</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2435</v>
+        <v>-0.3131</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0779</v>
+        <v>1.0698</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1646</v>
+        <v>5.3381</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1212</v>
+        <v>2.2092</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0434</v>
+        <v>3.1289</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.3302</v>
+        <v>-4.5814</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3647</v>
+        <v>-2.5223</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9654</v>
+        <v>-2.0591</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5744</v>
+        <v>0.5595</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7382</v>
+        <v>0.7476</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1638</v>
+        <v>-0.1881</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8671</v>
+        <v>4.9504</v>
       </c>
       <c r="W2" t="n">
-        <v>6.5184</v>
+        <v>6.6642</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6513</v>
+        <v>-1.7138</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1717</v>
+        <v>2.1377</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0717</v>
+        <v>2.2358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1</v>
+        <v>-0.0982</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6757</v>
+        <v>-0.6629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2148</v>
+        <v>0.271</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8905</v>
+        <v>-0.9339</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0252</v>
+        <v>1.1449</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8652</v>
+        <v>0.9828</v>
       </c>
       <c r="L3" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7009</v>
+        <v>-1.8078</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2393</v>
+        <v>1.2086</v>
       </c>
       <c r="T3" t="n">
-        <v>0.847</v>
+        <v>0.8436</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3922</v>
+        <v>0.365</v>
       </c>
       <c r="V3" t="n">
-        <v>1.008</v>
+        <v>1.0078</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1918</v>
+        <v>-0.2133</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4988</v>
+        <v>0.5123</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1237</v>
+        <v>1.1918</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6249</v>
+        <v>-0.6796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.531</v>
+        <v>0.5432</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5173</v>
+        <v>0.5563</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1815</v>
+        <v>1.2444</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1815</v>
+        <v>1.2444</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6505</v>
+        <v>-0.7013</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6642</v>
+        <v>-0.6882</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2323</v>
+        <v>-0.2257</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0578</v>
+        <v>-0.0526</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1745</v>
+        <v>-0.1731</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2081</v>
+        <v>0.226</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2563</v>
+        <v>3.586</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0482</v>
+        <v>-3.36</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9867</v>
+        <v>-0.9855</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4824</v>
+        <v>-0.47</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5043</v>
+        <v>-0.5155</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5508</v>
+        <v>1.7472</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0251</v>
+        <v>1.147</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5256</v>
+        <v>0.6002</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5375</v>
+        <v>-2.7327</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5075</v>
+        <v>-1.617</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0299</v>
+        <v>-1.1157</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6651</v>
+        <v>-0.6521</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5534</v>
+        <v>-0.5196</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1117</v>
+        <v>-0.1325</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2592</v>
+        <v>3.3321</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="6">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1949</v>
+        <v>0.192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1549</v>
+        <v>0.1515</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1756</v>
+        <v>0.1734</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1756</v>
+        <v>0.1734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0193</v>
+        <v>0.0186</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0193</v>
+        <v>0.0186</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0061</v>
+        <v>-0.0771</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0148</v>
+        <v>1.1125</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0209</v>
+        <v>-1.1896</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7393</v>
+        <v>-0.7955</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6449</v>
+        <v>0.6116</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3842</v>
+        <v>-1.4071</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3614</v>
+        <v>1.4281</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9594</v>
+        <v>2.0116</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1007</v>
+        <v>-2.2236</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3145</v>
+        <v>-1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7862</v>
+        <v>-0.8236</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2653</v>
+        <v>1.2363</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8537</v>
+        <v>0.8528</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4116</v>
+        <v>0.3836</v>
       </c>
       <c r="V7" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.871</v>
+        <v>-0.8985</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4078</v>
+        <v>-1.2915</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.393</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2718</v>
+        <v>0.2203</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4199</v>
+        <v>-0.4311</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6917</v>
+        <v>0.6514</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7016</v>
+        <v>0.7518</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7016</v>
+        <v>0.7518</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4298</v>
+        <v>-0.5315</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1215</v>
+        <v>-1.1829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6917</v>
+        <v>0.6514</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2579</v>
+        <v>1.218</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8914</v>
+        <v>0.8777</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3664</v>
+        <v>0.3403</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2396</v>
+        <v>-1.2822</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4285</v>
+        <v>-0.2634</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8111</v>
+        <v>-1.0188</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5622</v>
+        <v>-0.57</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9728</v>
+        <v>-1.0176</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4106</v>
+        <v>0.4476</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8673</v>
+        <v>0.9825</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3417</v>
+        <v>0.3823</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5256</v>
+        <v>0.6002</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4295</v>
+        <v>-1.5525</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3145</v>
+        <v>-1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1743</v>
+        <v>0.17</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0955</v>
+        <v>-0.0775</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2698</v>
+        <v>0.2475</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.243</v>
+        <v>-2.2018</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5283</v>
+        <v>-2.3642</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2853</v>
+        <v>0.1624</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1518</v>
+        <v>1.1056</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2217</v>
+        <v>-0.2592</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3735</v>
+        <v>1.3648</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0596</v>
+        <v>2.0963</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6998</v>
+        <v>0.7184</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3598</v>
+        <v>1.3779</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9907</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9215</v>
+        <v>-0.9776</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1939</v>
+        <v>-0.1916</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3867</v>
+        <v>-0.371</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1929</v>
+        <v>0.1794</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5682</v>
+        <v>-3.6306</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3567</v>
+        <v>-1.2487</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2115</v>
+        <v>-2.382</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8264</v>
+        <v>-2.8566</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5955</v>
+        <v>-0.605</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2309</v>
+        <v>-2.2516</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6544</v>
+        <v>-0.5777</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0164</v>
+        <v>0.0463</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.172</v>
+        <v>-2.2789</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5929</v>
+        <v>-1.6276</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0905</v>
+        <v>-1.0603</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7023</v>
+        <v>-0.671</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3882</v>
+        <v>-0.3893</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4149</v>
+        <v>-5.3923</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6458</v>
+        <v>-4.5279</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7691</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1156</v>
+        <v>-3.1253</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2709</v>
+        <v>-1.2921</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8447</v>
+        <v>-1.8332</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.994</v>
+        <v>-1.953</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.316</v>
+        <v>-1.2885</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1216</v>
+        <v>-1.1723</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5929</v>
+        <v>-0.6276</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5447</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1611</v>
+        <v>0.1546</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4512</v>
+        <v>-0.4328</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6123</v>
+        <v>0.5874</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.1845</v>
+        <v>-6.0295</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.5877</v>
+        <v>-6.1106</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4032</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.3447</v>
+        <v>-2.3295</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1694</v>
+        <v>-0.1298</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1753</v>
+        <v>-2.1997</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6852</v>
+        <v>-0.4613</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2669</v>
+        <v>1.4267</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9521</v>
+        <v>-1.888</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6595</v>
+        <v>-1.8682</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4363</v>
+        <v>-1.5565</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2232</v>
+        <v>-0.3117</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.8014</v>
+        <v>-4.6737</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.002</v>
+        <v>-6.8158</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1019</v>
+        <v>0.0837</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.36</v>
+        <v>-0.3341</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4619</v>
+        <v>0.4178</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.177299999999999</v>
+        <v>-8.230099999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>2.772799999999998</v>
+        <v>4.9155</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.9502</v>
+        <v>-13.1458</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.286</v>
+        <v>-8.5261</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.9991</v>
+        <v>-3.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.2869</v>
+        <v>-5.4471</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6184</v>
+        <v>11.7818</v>
       </c>
       <c r="K14" t="n">
-        <v>9.467999999999996</v>
+        <v>10.256</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1503</v>
+        <v>1.5258</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.9044</v>
+        <v>-20.308</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.467</v>
+        <v>-13.3352</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.4371</v>
+        <v>-6.9729</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.002500000000001</v>
+        <v>-8.763200000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.006</v>
+        <v>-20.4473</v>
       </c>
       <c r="R14" t="n">
-        <v>12.0035</v>
+        <v>11.6841</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6117</v>
+        <v>2.5196</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7233999999999997</v>
+        <v>0.8631</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8882</v>
+        <v>1.6566</v>
       </c>
       <c r="V14" t="n">
-        <v>6.499499999999999</v>
+        <v>6.539499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>12.437</v>
+        <v>12.7179</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.937500000000001</v>
+        <v>-6.1784</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SANDÁ C.B. L´HOSPITALET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SANDÁ C.B. L´HOSPITALET.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.213900000000001</v>
+        <v>8.094200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5552</v>
+        <v>12.3798</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.3412</v>
+        <v>-4.2856</v>
       </c>
       <c r="G2" t="n">
         <v>0.7567</v>
@@ -610,13 +610,13 @@
         <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5595</v>
+        <v>0.4398</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7476</v>
+        <v>0.5722</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1881</v>
+        <v>-0.1325</v>
       </c>
       <c r="V2" t="n">
         <v>4.9504</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1377</v>
+        <v>1.4623</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2358</v>
+        <v>1.6996</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0982</v>
+        <v>-0.2373</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6629</v>
@@ -688,13 +688,13 @@
         <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2086</v>
+        <v>0.5332</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8436</v>
+        <v>0.3073</v>
       </c>
       <c r="U3" t="n">
-        <v>0.365</v>
+        <v>0.2259</v>
       </c>
       <c r="V3" t="n">
         <v>1.0078</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5123</v>
+        <v>0.9594</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1918</v>
+        <v>4.2081</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6796</v>
+        <v>-3.2487</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5432</v>
+        <v>-0.9855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5563</v>
+        <v>-0.47</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0131</v>
+        <v>-0.5155</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2444</v>
+        <v>1.7472</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2444</v>
+        <v>1.147</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6002</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7013</v>
+        <v>-2.7327</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6882</v>
+        <v>-1.617</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0131</v>
+        <v>-1.1157</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1947</v>
+        <v>1.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2257</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0526</v>
+        <v>0.1025</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1731</v>
+        <v>-0.0212</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.3321</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.226</v>
+        <v>0.8507</v>
       </c>
       <c r="E5" t="n">
-        <v>3.586</v>
+        <v>1.3912</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.36</v>
+        <v>-0.5405</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9855</v>
+        <v>0.5432</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.47</v>
+        <v>0.5563</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5155</v>
+        <v>-0.0131</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7472</v>
+        <v>1.2444</v>
       </c>
       <c r="K5" t="n">
-        <v>1.147</v>
+        <v>1.2444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7327</v>
+        <v>-0.7013</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.617</v>
+        <v>-0.6882</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1157</v>
+        <v>-0.0131</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9737</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9474</v>
+        <v>0.1947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6521</v>
+        <v>0.1128</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5196</v>
+        <v>0.1467</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1325</v>
+        <v>-0.0339</v>
       </c>
       <c r="V5" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3321</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.192</v>
+        <v>0.2198</v>
       </c>
       <c r="E6" t="n">
         <v>0.0405</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1515</v>
+        <v>0.1793</v>
       </c>
       <c r="G6" t="n">
         <v>0.1734</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0186</v>
+        <v>0.0464</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0186</v>
+        <v>0.0464</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0771</v>
+        <v>-0.8243</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1125</v>
+        <v>0.4766</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1896</v>
+        <v>-1.3009</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7955</v>
@@ -1000,13 +1000,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2363</v>
+        <v>0.4891</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8528</v>
+        <v>0.2169</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3836</v>
+        <v>0.2722</v>
       </c>
       <c r="V7" t="n">
         <v>0.06619999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8985</v>
+        <v>-1.2192</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2915</v>
+        <v>-1.5287</v>
       </c>
       <c r="F8" t="n">
-        <v>0.393</v>
+        <v>0.3095</v>
       </c>
       <c r="G8" t="n">
         <v>0.2203</v>
@@ -1078,13 +1078,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1.218</v>
+        <v>0.8973</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8777</v>
+        <v>0.6405</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3403</v>
+        <v>0.2568</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2822</v>
+        <v>-1.3263</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2634</v>
+        <v>-0.3631</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0188</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.57</v>
@@ -1156,13 +1156,13 @@
         <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>0.17</v>
+        <v>0.126</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0775</v>
+        <v>-0.1772</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2475</v>
+        <v>0.3032</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4927</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2018</v>
+        <v>-1.7915</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3642</v>
+        <v>-2.0651</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1624</v>
+        <v>0.2737</v>
       </c>
       <c r="G10" t="n">
         <v>1.1056</v>
@@ -1234,13 +1234,13 @@
         <v>0.9737</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1916</v>
+        <v>0.2187</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.371</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1794</v>
+        <v>0.2907</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6306</v>
+        <v>-3.3138</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2487</v>
+        <v>-0.9875</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.382</v>
+        <v>-2.3263</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8566</v>
@@ -1312,13 +1312,13 @@
         <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0603</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.671</v>
+        <v>-0.4098</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3893</v>
+        <v>-0.3336</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4927</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VICENS MOREY</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3923</v>
+        <v>-5.2916</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5279</v>
+        <v>-5.2892</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.0024</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1253</v>
+        <v>-2.3295</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2921</v>
+        <v>-0.1298</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8332</v>
+        <v>-2.1997</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.953</v>
+        <v>-0.4613</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6645</v>
+        <v>1.4267</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2885</v>
+        <v>-1.888</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1723</v>
+        <v>-1.8682</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6276</v>
+        <v>-1.5565</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5447</v>
+        <v>-0.3117</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1421</v>
+        <v>-4.6737</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1421</v>
+        <v>-6.8158</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1546</v>
+        <v>0.8216</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4328</v>
+        <v>0.4873</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5874</v>
+        <v>0.3343</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2795</v>
+        <v>0.89</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2795</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>A. VICENS MOREY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0295</v>
+        <v>-5.4318</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1106</v>
+        <v>-4.4283</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08110000000000001</v>
+        <v>-1.0035</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.3295</v>
+        <v>-3.1253</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1298</v>
+        <v>-1.2921</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1997</v>
+        <v>-1.8332</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4613</v>
+        <v>-1.953</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4267</v>
+        <v>-0.6645</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.888</v>
+        <v>-1.2885</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8682</v>
+        <v>-1.1723</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5565</v>
+        <v>-0.6276</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3117</v>
+        <v>-0.5447</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.6737</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.8158</v>
+        <v>-2.1421</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1421</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0837</v>
+        <v>0.1151</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3341</v>
+        <v>-0.3332</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4178</v>
+        <v>0.4483</v>
       </c>
       <c r="V13" t="n">
-        <v>0.89</v>
+        <v>-0.2795</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5005</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6105</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.230099999999997</v>
+        <v>-7.6121</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9155</v>
+        <v>5.533899999999996</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.1458</v>
+        <v>-13.1459</v>
       </c>
       <c r="G14" t="n">
         <v>-8.5261</v>
@@ -1546,10 +1546,10 @@
         <v>11.6841</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5196</v>
+        <v>3.1378</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8631</v>
+        <v>1.4812</v>
       </c>
       <c r="U14" t="n">
         <v>1.6566</v>
